--- a/etf_holdings/2026-08-27_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-27_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:54</t>
+          <t>2026-08-27 16:57:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:54</t>
+          <t>2026-08-27 16:57:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:54</t>
+          <t>2026-08-27 16:57:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:54</t>
+          <t>2026-08-27 16:57:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:54</t>
+          <t>2026-08-27 16:57:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:54</t>
+          <t>2026-08-27 16:57:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:54</t>
+          <t>2026-08-27 16:57:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:54</t>
+          <t>2026-08-27 16:57:19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:54</t>
+          <t>2026-08-27 16:57:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:54</t>
+          <t>2026-08-27 16:57:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:54</t>
+          <t>2026-08-27 16:57:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:54</t>
+          <t>2026-08-27 16:57:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:54</t>
+          <t>2026-08-27 16:57:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:54</t>
+          <t>2026-08-27 16:57:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:54</t>
+          <t>2026-08-27 16:57:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:55</t>
+          <t>2026-08-27 16:57:20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:55</t>
+          <t>2026-08-27 16:57:20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:55</t>
+          <t>2026-08-27 16:57:20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:55</t>
+          <t>2026-08-27 16:57:20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:55</t>
+          <t>2026-08-27 16:57:20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:55</t>
+          <t>2026-08-27 16:57:20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:55</t>
+          <t>2026-08-27 16:57:20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:55</t>
+          <t>2026-08-27 16:57:20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:55</t>
+          <t>2026-08-27 16:57:20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:55</t>
+          <t>2026-08-27 16:57:20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:55</t>
+          <t>2026-08-27 16:57:20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:55</t>
+          <t>2026-08-27 16:57:20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:55</t>
+          <t>2026-08-27 16:57:20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:55</t>
+          <t>2026-08-27 16:57:20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:55</t>
+          <t>2026-08-27 16:57:20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:56</t>
+          <t>2026-08-27 16:57:22</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:56</t>
+          <t>2026-08-27 16:57:22</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:56</t>
+          <t>2026-08-27 16:57:22</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:56</t>
+          <t>2026-08-27 16:57:22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:56</t>
+          <t>2026-08-27 16:57:22</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:56</t>
+          <t>2026-08-27 16:57:22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:56</t>
+          <t>2026-08-27 16:57:22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:56</t>
+          <t>2026-08-27 16:57:22</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:56</t>
+          <t>2026-08-27 16:57:22</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:56</t>
+          <t>2026-08-27 16:57:22</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:56</t>
+          <t>2026-08-27 16:57:22</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-27_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-27_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:19</t>
+          <t>2026-08-27 17:14:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.65%260,000</t>
+          <t>8.52%260,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.65%</t>
+          <t>8.52%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:19</t>
+          <t>2026-08-27 17:14:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.25%1,001,000</t>
+          <t>7.64%1,001,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.25%</t>
+          <t>7.64%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:19</t>
+          <t>2026-08-27 17:14:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.24%1,306,000</t>
+          <t>7.20%1,306,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.24%</t>
+          <t>7.20%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:19</t>
+          <t>2026-08-27 17:14:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.61%2,482,000</t>
+          <t>6.70%2,482,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.61%</t>
+          <t>6.70%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:19</t>
+          <t>2026-08-27 17:14:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.29%465,000</t>
+          <t>5.85%465,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.29%</t>
+          <t>5.85%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:19</t>
+          <t>2026-08-27 17:14:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.34%1,161,000</t>
+          <t>5.45%1,161,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.34%</t>
+          <t>5.45%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:19</t>
+          <t>2026-08-27 17:14:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+1.7%2090</t>
+          <t>+9.94%6915</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2090</v>
+        <v>6915</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.06%1,074,000</t>
+          <t>5.42%343,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.06%</t>
+          <t>5.42%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1074000</v>
+        <v>343000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:19</t>
+          <t>2026-08-27 17:14:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+9.94%6915</t>
+          <t>+1.7%2090</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>+1.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6915</v>
+        <v>2090</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.95%343,000</t>
+          <t>5.13%1,074,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.95%</t>
+          <t>5.13%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>343000</v>
+        <v>1074000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:19</t>
+          <t>2026-08-27 17:14:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.47%1,630,000</t>
+          <t>4.88%1,630,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.47%</t>
+          <t>4.88%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:19</t>
+          <t>2026-08-27 17:14:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>6584南俊國際</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+0.99%5090</t>
+          <t>+2.65%620</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>+2.65%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5090</v>
+        <v>620</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.10%268,000</t>
+          <t>3.16%2,231,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.16%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>268000</v>
+        <v>2231000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:19</t>
+          <t>2026-08-27 17:14:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6584南俊國際</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+2.65%620</t>
+          <t>+0.99%5090</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>620</v>
+        <v>5090</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.09%2,231,000</t>
+          <t>3.12%268,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.12%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>2231000</v>
+        <v>268000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:19</t>
+          <t>2026-08-27 17:14:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.02%7,245,000</t>
+          <t>2.97%7,245,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>2.97%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:19</t>
+          <t>2026-08-27 17:14:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.94%10,877,000</t>
+          <t>2.90%10,877,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>2.90%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:19</t>
+          <t>2026-08-27 17:14:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+1.17%433</t>
+          <t>+9.9%227.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+1.17%</t>
+          <t>+9.9%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>433</v>
+        <v>227.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.70%2,753,000</t>
+          <t>2.83%5,445,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>2753000</v>
+        <v>5445000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:19</t>
+          <t>2026-08-27 17:14:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+9.9%227.5</t>
+          <t>+1.17%433</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+9.9%</t>
+          <t>+1.17%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>227.5</v>
+        <v>433</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.59%5,445,000</t>
+          <t>2.73%2,753,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.73%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>5445000</v>
+        <v>2753000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:20</t>
+          <t>2026-08-27 17:14:16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.58%2,682,000</t>
+          <t>2.59%2,682,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.59%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:20</t>
+          <t>2026-08-27 17:14:16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.54%632,000</t>
+          <t>2.56%632,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.56%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:20</t>
+          <t>2026-08-27 17:14:16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.41%266,000</t>
+          <t>2.35%266,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.35%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:20</t>
+          <t>2026-08-27 17:14:16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.30%164,000</t>
+          <t>2.22%164,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:20</t>
+          <t>2026-08-27 17:14:16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1681,12 +1681,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.95%215,000</t>
+          <t>1.90%215,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.90%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:20</t>
+          <t>2026-08-27 17:14:16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.71%844,013</t>
+          <t>1.76%844,013</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.76%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:20</t>
+          <t>2026-08-27 17:14:16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:20</t>
+          <t>2026-08-27 17:14:16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1864,12 +1864,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.04%1,000,000</t>
+          <t>1.09%1,000,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:20</t>
+          <t>2026-08-27 17:14:16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.97%716,000</t>
+          <t>0.99%716,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:20</t>
+          <t>2026-08-27 17:14:16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.81%300,000</t>
+          <t>0.89%300,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:20</t>
+          <t>2026-08-27 17:14:16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-3.43%563</t>
+          <t>+3.53%3370</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-3.43%</t>
+          <t>+3.53%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>563</v>
+        <v>3370</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.50%373,000</t>
+          <t>0.49%63,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>373000</v>
+        <v>63000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:20</t>
+          <t>2026-08-27 17:14:16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+3.53%3370</t>
+          <t>-3.43%563</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+3.53%</t>
+          <t>-3.43%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>3370</v>
+        <v>563</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.47%63,000</t>
+          <t>0.48%373,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>63000</v>
+        <v>373000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:20</t>
+          <t>2026-08-27 17:14:16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.46%659,000</t>
+          <t>0.45%659,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:20</t>
+          <t>2026-08-27 17:14:16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.46%250,000</t>
+          <t>0.45%250,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:20</t>
+          <t>2026-08-27 17:14:16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,25 +2273,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2357華碩</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.31%968</t>
+          <t>+10%1430</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>+10%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>968</v>
+        <v>1430</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.44%196,000</t>
+          <t>0.44%134,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2300,11 +2300,11 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>196000</v>
+        <v>134000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:22</t>
+          <t>2026-08-27 17:14:17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,25 +2334,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>2357華碩</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.4%5645</t>
+          <t>-0.31%968</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>5645</v>
+        <v>968</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.43%33,000</t>
+          <t>0.43%196,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2361,11 +2361,11 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>33000</v>
+        <v>196000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:22</t>
+          <t>2026-08-27 17:14:17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,34 +2395,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-1.85%345</t>
+          <t>-1.4%5645</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>345</v>
+        <v>5645</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.41%508,000</t>
+          <t>0.43%33,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>508000</v>
+        <v>33000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:22</t>
+          <t>2026-08-27 17:14:17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.41%1,957,000</t>
+          <t>0.40%1,957,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:22</t>
+          <t>2026-08-27 17:14:17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,25 +2517,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+10%1430</t>
+          <t>+9.93%675</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+9.93%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1430</v>
+        <v>675</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.40%134,000</t>
+          <t>0.40%261,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>134000</v>
+        <v>261000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:22</t>
+          <t>2026-08-27 17:14:17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-5.56%1445</t>
+          <t>-1.85%345</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-5.56%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1445</v>
+        <v>345</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.40%113,000</t>
+          <t>0.40%508,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2605,11 +2605,11 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>113000</v>
+        <v>508000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:22</t>
+          <t>2026-08-27 17:14:17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2657,12 +2657,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.40%11,000</t>
+          <t>0.38%11,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:22</t>
+          <t>2026-08-27 17:14:17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:22</t>
+          <t>2026-08-27 17:14:17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,25 +2761,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+9.93%675</t>
+          <t>-5.56%1445</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+9.93%</t>
+          <t>-5.56%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>675</v>
+        <v>1445</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.37%261,000</t>
+          <t>0.37%113,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2788,11 +2788,11 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>261000</v>
+        <v>113000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:22</t>
+          <t>2026-08-27 17:14:17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:22</t>
+          <t>2026-08-27 17:14:17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.34%98,000</t>
+          <t>0.34%99,952</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>98000</v>
+        <v>99952</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:22</t>
+          <t>2026-08-27 17:14:17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-27_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-27_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:15</t>
+          <t>2026-08-27 19:38:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:15</t>
+          <t>2026-08-27 19:38:16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:15</t>
+          <t>2026-08-27 19:38:16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:15</t>
+          <t>2026-08-27 19:38:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:15</t>
+          <t>2026-08-27 19:38:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:15</t>
+          <t>2026-08-27 19:38:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:15</t>
+          <t>2026-08-27 19:38:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:15</t>
+          <t>2026-08-27 19:38:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:15</t>
+          <t>2026-08-27 19:38:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:15</t>
+          <t>2026-08-27 19:38:16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:15</t>
+          <t>2026-08-27 19:38:16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:15</t>
+          <t>2026-08-27 19:38:16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:15</t>
+          <t>2026-08-27 19:38:16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:15</t>
+          <t>2026-08-27 19:38:16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:15</t>
+          <t>2026-08-27 19:38:16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:16</t>
+          <t>2026-08-27 19:38:17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:16</t>
+          <t>2026-08-27 19:38:17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:16</t>
+          <t>2026-08-27 19:38:17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:16</t>
+          <t>2026-08-27 19:38:17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:16</t>
+          <t>2026-08-27 19:38:17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:16</t>
+          <t>2026-08-27 19:38:17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:16</t>
+          <t>2026-08-27 19:38:17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:16</t>
+          <t>2026-08-27 19:38:17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:16</t>
+          <t>2026-08-27 19:38:17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:16</t>
+          <t>2026-08-27 19:38:17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:16</t>
+          <t>2026-08-27 19:38:17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:16</t>
+          <t>2026-08-27 19:38:17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:16</t>
+          <t>2026-08-27 19:38:17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:16</t>
+          <t>2026-08-27 19:38:17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:16</t>
+          <t>2026-08-27 19:38:17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:17</t>
+          <t>2026-08-27 19:38:18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:17</t>
+          <t>2026-08-27 19:38:18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:17</t>
+          <t>2026-08-27 19:38:18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:17</t>
+          <t>2026-08-27 19:38:18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:17</t>
+          <t>2026-08-27 19:38:18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:17</t>
+          <t>2026-08-27 19:38:18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:17</t>
+          <t>2026-08-27 19:38:18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:17</t>
+          <t>2026-08-27 19:38:18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:17</t>
+          <t>2026-08-27 19:38:18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:17</t>
+          <t>2026-08-27 19:38:18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:17</t>
+          <t>2026-08-27 19:38:18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-27_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-27_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:16</t>
+          <t>2026-08-27 22:49:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:16</t>
+          <t>2026-08-27 22:49:31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:16</t>
+          <t>2026-08-27 22:49:31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:16</t>
+          <t>2026-08-27 22:49:31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:16</t>
+          <t>2026-08-27 22:49:31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:16</t>
+          <t>2026-08-27 22:49:31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:16</t>
+          <t>2026-08-27 22:49:31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:16</t>
+          <t>2026-08-27 22:49:31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:16</t>
+          <t>2026-08-27 22:49:31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:16</t>
+          <t>2026-08-27 22:49:31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:16</t>
+          <t>2026-08-27 22:49:31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:16</t>
+          <t>2026-08-27 22:49:31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:16</t>
+          <t>2026-08-27 22:49:31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:16</t>
+          <t>2026-08-27 22:49:31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:16</t>
+          <t>2026-08-27 22:49:31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:17</t>
+          <t>2026-08-27 22:49:33</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:17</t>
+          <t>2026-08-27 22:49:33</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:17</t>
+          <t>2026-08-27 22:49:33</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:17</t>
+          <t>2026-08-27 22:49:33</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:17</t>
+          <t>2026-08-27 22:49:33</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:17</t>
+          <t>2026-08-27 22:49:33</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:17</t>
+          <t>2026-08-27 22:49:33</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:17</t>
+          <t>2026-08-27 22:49:33</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:17</t>
+          <t>2026-08-27 22:49:33</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:17</t>
+          <t>2026-08-27 22:49:33</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:17</t>
+          <t>2026-08-27 22:49:33</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:17</t>
+          <t>2026-08-27 22:49:33</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:17</t>
+          <t>2026-08-27 22:49:33</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:17</t>
+          <t>2026-08-27 22:49:33</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:17</t>
+          <t>2026-08-27 22:49:33</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:18</t>
+          <t>2026-08-27 22:49:34</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:18</t>
+          <t>2026-08-27 22:49:34</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:18</t>
+          <t>2026-08-27 22:49:34</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:18</t>
+          <t>2026-08-27 22:49:34</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:18</t>
+          <t>2026-08-27 22:49:34</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:18</t>
+          <t>2026-08-27 22:49:34</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:18</t>
+          <t>2026-08-27 22:49:34</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:18</t>
+          <t>2026-08-27 22:49:34</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:18</t>
+          <t>2026-08-27 22:49:34</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:18</t>
+          <t>2026-08-27 22:49:34</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-27 19:38:18</t>
+          <t>2026-08-27 22:49:34</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
